--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/86.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/86.xlsx
@@ -426,13 +426,13 @@
         <v>-10.19099547921018</v>
       </c>
       <c r="E2">
-        <v>-10.04595975837551</v>
+        <v>-8.70088976624722</v>
       </c>
       <c r="F2">
-        <v>4.794006233037987</v>
+        <v>4.673858383763172</v>
       </c>
       <c r="G2">
-        <v>-15.00753171656944</v>
+        <v>-16.19332278109883</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.550312250361621</v>
       </c>
       <c r="E3">
-        <v>-10.39114268961018</v>
+        <v>-8.373915828997388</v>
       </c>
       <c r="F3">
-        <v>4.505743249721529</v>
+        <v>4.571566818684938</v>
       </c>
       <c r="G3">
-        <v>-13.66597286332627</v>
+        <v>-15.24309358441628</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.915020895871219</v>
       </c>
       <c r="E4">
-        <v>-10.03136448664879</v>
+        <v>-10.21588621703933</v>
       </c>
       <c r="F4">
-        <v>4.474130895943442</v>
+        <v>4.892924504516334</v>
       </c>
       <c r="G4">
-        <v>-13.38278217680593</v>
+        <v>-13.86768605830683</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.353085051407204</v>
       </c>
       <c r="E5">
-        <v>-9.850873098125069</v>
+        <v>-11.20707407936421</v>
       </c>
       <c r="F5">
-        <v>4.625639289755788</v>
+        <v>5.348072082378139</v>
       </c>
       <c r="G5">
-        <v>-13.4001790936148</v>
+        <v>-14.07894686662265</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.852075936796677</v>
       </c>
       <c r="E6">
-        <v>-12.33625813012483</v>
+        <v>-13.05882144278871</v>
       </c>
       <c r="F6">
-        <v>4.932346112163453</v>
+        <v>4.92564861984706</v>
       </c>
       <c r="G6">
-        <v>-11.92910838832979</v>
+        <v>-12.92511249818384</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.419020371011938</v>
       </c>
       <c r="E7">
-        <v>-12.5986107432852</v>
+        <v>-11.24987721568471</v>
       </c>
       <c r="F7">
-        <v>5.410232539559137</v>
+        <v>5.406922594195868</v>
       </c>
       <c r="G7">
-        <v>-11.88338975443246</v>
+        <v>-14.33106477271139</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.024507532848745</v>
       </c>
       <c r="E8">
-        <v>-13.38690938464443</v>
+        <v>-13.5981355262582</v>
       </c>
       <c r="F8">
-        <v>5.217851863481131</v>
+        <v>5.862317230180482</v>
       </c>
       <c r="G8">
-        <v>-10.14669742780403</v>
+        <v>-11.31654159447075</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.657961601496114</v>
       </c>
       <c r="E9">
-        <v>-14.30223172191881</v>
+        <v>-14.26732624426768</v>
       </c>
       <c r="F9">
-        <v>5.232371279313879</v>
+        <v>5.913106678888624</v>
       </c>
       <c r="G9">
-        <v>-9.513966101065286</v>
+        <v>-10.89550972333178</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.286899044643234</v>
       </c>
       <c r="E10">
-        <v>-14.80232016353386</v>
+        <v>-13.01319253868743</v>
       </c>
       <c r="F10">
-        <v>5.270994699179616</v>
+        <v>6.029008612604145</v>
       </c>
       <c r="G10">
-        <v>-9.254363051512255</v>
+        <v>-10.90581545159553</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.891201929459433</v>
       </c>
       <c r="E11">
-        <v>-14.91039672420092</v>
+        <v>-13.74461354651031</v>
       </c>
       <c r="F11">
-        <v>5.51430260638041</v>
+        <v>5.901806937181965</v>
       </c>
       <c r="G11">
-        <v>-7.556423970966536</v>
+        <v>-8.821088782969062</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.454128150459277</v>
       </c>
       <c r="E12">
-        <v>-15.85672552300582</v>
+        <v>-16.58168439841976</v>
       </c>
       <c r="F12">
-        <v>5.415895871912748</v>
+        <v>6.22518226434963</v>
       </c>
       <c r="G12">
-        <v>-7.066555926429499</v>
+        <v>-8.321305654541908</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.95595827137539</v>
       </c>
       <c r="E13">
-        <v>-15.58271208927569</v>
+        <v>-14.12290867968907</v>
       </c>
       <c r="F13">
-        <v>5.664523447283503</v>
+        <v>6.203946351729502</v>
       </c>
       <c r="G13">
-        <v>-6.083072299804972</v>
+        <v>-8.111033044069559</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.399487735138449</v>
       </c>
       <c r="E14">
-        <v>-16.48808084068121</v>
+        <v>-17.0318192432562</v>
       </c>
       <c r="F14">
-        <v>5.510297414120263</v>
+        <v>6.734844167232691</v>
       </c>
       <c r="G14">
-        <v>-6.161833488729774</v>
+        <v>-7.517263527782497</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.780529936974437</v>
       </c>
       <c r="E15">
-        <v>-17.45271825989912</v>
+        <v>-17.89876389270664</v>
       </c>
       <c r="F15">
-        <v>6.01266160014498</v>
+        <v>6.566469305420915</v>
       </c>
       <c r="G15">
-        <v>-5.30420356132618</v>
+        <v>-6.119501542919113</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.11289576722518</v>
       </c>
       <c r="E16">
-        <v>-18.42449708262713</v>
+        <v>-20.22890377877544</v>
       </c>
       <c r="F16">
-        <v>5.889982988817294</v>
+        <v>6.416956381062024</v>
       </c>
       <c r="G16">
-        <v>-4.990095690014591</v>
+        <v>-6.133942142561414</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.41596901714159</v>
       </c>
       <c r="E17">
-        <v>-18.46091507059681</v>
+        <v>-19.94702438569399</v>
       </c>
       <c r="F17">
-        <v>5.786977172371197</v>
+        <v>6.539712593979566</v>
       </c>
       <c r="G17">
-        <v>-4.365213666749457</v>
+        <v>-5.266231603990739</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.715691464511066</v>
       </c>
       <c r="E18">
-        <v>-19.51501249383625</v>
+        <v>-19.91679229321878</v>
       </c>
       <c r="F18">
-        <v>6.099569045960634</v>
+        <v>6.484479266472699</v>
       </c>
       <c r="G18">
-        <v>-4.335028112522383</v>
+        <v>-5.853850126665836</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.051442697432</v>
       </c>
       <c r="E19">
-        <v>-21.40113097497897</v>
+        <v>-20.19331450154916</v>
       </c>
       <c r="F19">
-        <v>6.225758733302849</v>
+        <v>7.005341137589748</v>
       </c>
       <c r="G19">
-        <v>-3.905570902985967</v>
+        <v>-5.482055999332445</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4558709467277116</v>
       </c>
       <c r="E20">
-        <v>-21.46251896862695</v>
+        <v>-20.80760200068964</v>
       </c>
       <c r="F20">
-        <v>6.172569970132816</v>
+        <v>6.829731907156245</v>
       </c>
       <c r="G20">
-        <v>-3.185676222743751</v>
+        <v>-3.878351597562079</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.03007700022620947</v>
       </c>
       <c r="E21">
-        <v>-20.84982096386316</v>
+        <v>-22.4502063205439</v>
       </c>
       <c r="F21">
-        <v>6.350895256211298</v>
+        <v>5.926560260640283</v>
       </c>
       <c r="G21">
-        <v>-3.211491856858988</v>
+        <v>-5.306239546832831</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.3812804340381201</v>
       </c>
       <c r="E22">
-        <v>-22.96781995656864</v>
+        <v>-21.7935187192696</v>
       </c>
       <c r="F22">
-        <v>5.939508640204916</v>
+        <v>6.524733903431339</v>
       </c>
       <c r="G22">
-        <v>-2.574532963466594</v>
+        <v>-2.553355403651876</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.5768978720181341</v>
       </c>
       <c r="E23">
-        <v>-22.14073493533371</v>
+        <v>-21.46968301450708</v>
       </c>
       <c r="F23">
-        <v>5.467881018587049</v>
+        <v>6.295676182057671</v>
       </c>
       <c r="G23">
-        <v>-2.643935240151875</v>
+        <v>-3.642799661351856</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6104107344823211</v>
       </c>
       <c r="E24">
-        <v>-21.76020726446917</v>
+        <v>-23.30713398548937</v>
       </c>
       <c r="F24">
-        <v>5.529612291464963</v>
+        <v>6.513844341556778</v>
       </c>
       <c r="G24">
-        <v>-2.402957319802786</v>
+        <v>-3.163399561809995</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.4907331328018619</v>
       </c>
       <c r="E25">
-        <v>-23.19354627195497</v>
+        <v>-23.90434460914692</v>
       </c>
       <c r="F25">
-        <v>5.481391613751662</v>
+        <v>6.217403100892991</v>
       </c>
       <c r="G25">
-        <v>-2.176582215827422</v>
+        <v>-2.546919703123533</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2302093093846766</v>
       </c>
       <c r="E26">
-        <v>-23.63795259717171</v>
+        <v>-24.65014352194417</v>
       </c>
       <c r="F26">
-        <v>4.89157835448821</v>
+        <v>5.935292815058016</v>
       </c>
       <c r="G26">
-        <v>-1.609515559860121</v>
+        <v>-2.555566848072109</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1416532230143983</v>
       </c>
       <c r="E27">
-        <v>-22.99901208553347</v>
+        <v>-24.88280745951025</v>
       </c>
       <c r="F27">
-        <v>5.072969695218983</v>
+        <v>5.739302873198723</v>
       </c>
       <c r="G27">
-        <v>-1.530578912021739</v>
+        <v>-3.136852297130579</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.6013471624002839</v>
       </c>
       <c r="E28">
-        <v>-23.25455387378631</v>
+        <v>-23.73882888416658</v>
       </c>
       <c r="F28">
-        <v>5.07384231717839</v>
+        <v>5.892491578987349</v>
       </c>
       <c r="G28">
-        <v>-2.279497145006745</v>
+        <v>-2.259319369944888</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.116337584538003</v>
       </c>
       <c r="E29">
-        <v>-22.34582046619309</v>
+        <v>-22.93128875674876</v>
       </c>
       <c r="F29">
-        <v>4.861001744378822</v>
+        <v>5.514161656553935</v>
       </c>
       <c r="G29">
-        <v>-1.410227339487074</v>
+        <v>-1.317578412025031</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.66618182087356</v>
       </c>
       <c r="E30">
-        <v>-22.35315206561151</v>
+        <v>-24.10772743377942</v>
       </c>
       <c r="F30">
-        <v>5.059650728470137</v>
+        <v>5.927109806592941</v>
       </c>
       <c r="G30">
-        <v>-1.991108901989754</v>
+        <v>-2.595922398195825</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.232762897570671</v>
       </c>
       <c r="E31">
-        <v>-21.59114121586681</v>
+        <v>-24.15691571845073</v>
       </c>
       <c r="F31">
-        <v>5.1247616297716</v>
+        <v>5.359401914497193</v>
       </c>
       <c r="G31">
-        <v>-1.83873111190818</v>
+        <v>-1.9617344314198</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.803007873160588</v>
       </c>
       <c r="E32">
-        <v>-21.57989701490576</v>
+        <v>-23.6439664106539</v>
       </c>
       <c r="F32">
-        <v>5.231067889345472</v>
+        <v>5.587389050672025</v>
       </c>
       <c r="G32">
-        <v>-2.123765772293889</v>
+        <v>-2.63546355411688</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.374926524781718</v>
       </c>
       <c r="E33">
-        <v>-22.15762614338232</v>
+        <v>-23.91375930660887</v>
       </c>
       <c r="F33">
-        <v>4.995390277245266</v>
+        <v>5.399146598151061</v>
       </c>
       <c r="G33">
-        <v>-2.153497781782084</v>
+        <v>-4.150849221990569</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.939188792553622</v>
       </c>
       <c r="E34">
-        <v>-21.70099293834487</v>
+        <v>-21.36674174336472</v>
       </c>
       <c r="F34">
-        <v>4.980302310988875</v>
+        <v>5.781073116718438</v>
       </c>
       <c r="G34">
-        <v>-2.581233507638078</v>
+        <v>-3.394273697173229</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.50024734127728</v>
       </c>
       <c r="E35">
-        <v>-20.43839551484428</v>
+        <v>-20.68342671492531</v>
       </c>
       <c r="F35">
-        <v>5.592555099368188</v>
+        <v>5.827654658809259</v>
       </c>
       <c r="G35">
-        <v>-3.240392919416825</v>
+        <v>-3.387967107920917</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.051361637699185</v>
       </c>
       <c r="E36">
-        <v>-19.08603920803765</v>
+        <v>-21.48973962588705</v>
       </c>
       <c r="F36">
-        <v>5.572825291073643</v>
+        <v>6.067616195410729</v>
       </c>
       <c r="G36">
-        <v>-3.171454119107042</v>
+        <v>-3.458034804259591</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.590823160010177</v>
       </c>
       <c r="E37">
-        <v>-19.90143623785877</v>
+        <v>-20.92165161857282</v>
       </c>
       <c r="F37">
-        <v>5.601702584735766</v>
+        <v>5.855744850631408</v>
       </c>
       <c r="G37">
-        <v>-3.656842995529444</v>
+        <v>-5.444229706000733</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.116861698484865</v>
       </c>
       <c r="E38">
-        <v>-19.40328598311901</v>
+        <v>-19.31701402479888</v>
       </c>
       <c r="F38">
-        <v>5.983937925956654</v>
+        <v>6.150594466850178</v>
       </c>
       <c r="G38">
-        <v>-4.176519192102078</v>
+        <v>-4.518885880136886</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.619681074121343</v>
       </c>
       <c r="E39">
-        <v>-17.85303536217718</v>
+        <v>-19.2960064338773</v>
       </c>
       <c r="F39">
-        <v>5.979102871796817</v>
+        <v>6.567219982024834</v>
       </c>
       <c r="G39">
-        <v>-4.57019933599559</v>
+        <v>-5.958095895151946</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.103553759676411</v>
       </c>
       <c r="E40">
-        <v>-17.24444468333835</v>
+        <v>-18.4200546496256</v>
       </c>
       <c r="F40">
-        <v>5.937671541343006</v>
+        <v>6.573995075931084</v>
       </c>
       <c r="G40">
-        <v>-4.14257947923347</v>
+        <v>-4.511771517772993</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.558893104720028</v>
       </c>
       <c r="E41">
-        <v>-17.72852949781029</v>
+        <v>-18.15333658752183</v>
       </c>
       <c r="F41">
-        <v>6.027163595212659</v>
+        <v>6.915711301305453</v>
       </c>
       <c r="G41">
-        <v>-4.754487474530199</v>
+        <v>-6.4918518419031</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.990190384386358</v>
       </c>
       <c r="E42">
-        <v>-16.68862431211089</v>
+        <v>-17.05431670212631</v>
       </c>
       <c r="F42">
-        <v>6.151210528451284</v>
+        <v>6.926230275995802</v>
       </c>
       <c r="G42">
-        <v>-4.592873262394058</v>
+        <v>-6.322504195387221</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.398646623967023</v>
       </c>
       <c r="E43">
-        <v>-14.68563950225223</v>
+        <v>-16.76358867083387</v>
       </c>
       <c r="F43">
-        <v>5.969466021301368</v>
+        <v>7.22159459663709</v>
       </c>
       <c r="G43">
-        <v>-5.419936922833561</v>
+        <v>-6.459080751609855</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.780339707699863</v>
       </c>
       <c r="E44">
-        <v>-16.06598630690027</v>
+        <v>-16.24674940386445</v>
       </c>
       <c r="F44">
-        <v>5.99376323745604</v>
+        <v>7.051073813309894</v>
       </c>
       <c r="G44">
-        <v>-6.370848091897199</v>
+        <v>-6.696509767140845</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.144512769846584</v>
       </c>
       <c r="E45">
-        <v>-14.26152074058985</v>
+        <v>-17.40332166542345</v>
       </c>
       <c r="F45">
-        <v>6.255396205804383</v>
+        <v>6.904593685779068</v>
       </c>
       <c r="G45">
-        <v>-5.915946029345945</v>
+        <v>-5.744396870046452</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.480882061270604</v>
       </c>
       <c r="E46">
-        <v>-14.14590427070002</v>
+        <v>-14.63624743625057</v>
       </c>
       <c r="F46">
-        <v>6.088429258551433</v>
+        <v>6.766548375953874</v>
       </c>
       <c r="G46">
-        <v>-6.416666042160712</v>
+        <v>-6.28067876304407</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.796530292814374</v>
       </c>
       <c r="E47">
-        <v>-13.43788188807477</v>
+        <v>-16.38158471744283</v>
       </c>
       <c r="F47">
-        <v>6.497300949564098</v>
+        <v>6.947535871676209</v>
       </c>
       <c r="G47">
-        <v>-6.566491401631509</v>
+        <v>-7.573277958306965</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.08671377374406</v>
       </c>
       <c r="E48">
-        <v>-13.08572963534229</v>
+        <v>-14.29826025021408</v>
       </c>
       <c r="F48">
-        <v>6.809815221563679</v>
+        <v>6.950562333680613</v>
       </c>
       <c r="G48">
-        <v>-7.138649676638209</v>
+        <v>-8.735577391689686</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.34528210677386</v>
       </c>
       <c r="E49">
-        <v>-12.47825296110934</v>
+        <v>-14.61515833279685</v>
       </c>
       <c r="F49">
-        <v>6.54378113447633</v>
+        <v>7.496278885434569</v>
       </c>
       <c r="G49">
-        <v>-6.219470086568485</v>
+        <v>-8.509066555347212</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.57765445239501</v>
       </c>
       <c r="E50">
-        <v>-12.86567296941356</v>
+        <v>-14.558570521597</v>
       </c>
       <c r="F50">
-        <v>6.646988081573688</v>
+        <v>6.779959197645814</v>
       </c>
       <c r="G50">
-        <v>-7.636774221750187</v>
+        <v>-7.565299543557321</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.77090544337285</v>
       </c>
       <c r="E51">
-        <v>-11.01362219823054</v>
+        <v>-13.98504834547356</v>
       </c>
       <c r="F51">
-        <v>6.447697696586618</v>
+        <v>7.180383401305524</v>
       </c>
       <c r="G51">
-        <v>-7.331383016843498</v>
+        <v>-7.700767067024299</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.93354465575771</v>
       </c>
       <c r="E52">
-        <v>-10.72002764289125</v>
+        <v>-11.97823697507841</v>
       </c>
       <c r="F52">
-        <v>6.517051346035543</v>
+        <v>7.375836466859484</v>
       </c>
       <c r="G52">
-        <v>-7.128065862549159</v>
+        <v>-8.446788572662443</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.05803377576017</v>
       </c>
       <c r="E53">
-        <v>-11.8555470287886</v>
+        <v>-12.85830061372907</v>
       </c>
       <c r="F53">
-        <v>6.644412975755183</v>
+        <v>7.40351806255545</v>
       </c>
       <c r="G53">
-        <v>-6.934074515038946</v>
+        <v>-8.001480471083998</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.14645278167455</v>
       </c>
       <c r="E54">
-        <v>-9.342117157259334</v>
+        <v>-14.22722207845576</v>
       </c>
       <c r="F54">
-        <v>6.305257602846079</v>
+        <v>7.30178396195945</v>
       </c>
       <c r="G54">
-        <v>-8.340894152497775</v>
+        <v>-8.346770370829981</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.20568025147818</v>
       </c>
       <c r="E55">
-        <v>-9.709313000645293</v>
+        <v>-10.96878124860659</v>
       </c>
       <c r="F55">
-        <v>6.58509843810423</v>
+        <v>7.460729438750699</v>
       </c>
       <c r="G55">
-        <v>-7.936895038158355</v>
+        <v>-8.74314198824692</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.22791464439871</v>
       </c>
       <c r="E56">
-        <v>-9.487820808456128</v>
+        <v>-10.71865098679292</v>
       </c>
       <c r="F56">
-        <v>6.698412596353922</v>
+        <v>7.60589509037171</v>
       </c>
       <c r="G56">
-        <v>-8.240203909920842</v>
+        <v>-7.831560100189825</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.22702774954675</v>
       </c>
       <c r="E57">
-        <v>-8.278931086686503</v>
+        <v>-10.8530742092366</v>
       </c>
       <c r="F57">
-        <v>6.590197971151945</v>
+        <v>7.520070899402216</v>
       </c>
       <c r="G57">
-        <v>-8.567981023764082</v>
+        <v>-8.052502598935245</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.19508427674287</v>
       </c>
       <c r="E58">
-        <v>-7.969020439497575</v>
+        <v>-11.65473184891846</v>
       </c>
       <c r="F58">
-        <v>6.559545343158613</v>
+        <v>7.306362455760986</v>
       </c>
       <c r="G58">
-        <v>-7.898009370254076</v>
+        <v>-10.26179847511341</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.1419045290672</v>
       </c>
       <c r="E59">
-        <v>-7.316662059374607</v>
+        <v>-9.413721388268618</v>
       </c>
       <c r="F59">
-        <v>7.086151315630961</v>
+        <v>7.484599054308203</v>
       </c>
       <c r="G59">
-        <v>-7.723341677056589</v>
+        <v>-8.846864690537826</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.07058496747038</v>
       </c>
       <c r="E60">
-        <v>-7.853883987852556</v>
+        <v>-8.195743019165599</v>
       </c>
       <c r="F60">
-        <v>6.821156139624141</v>
+        <v>6.953172281029258</v>
       </c>
       <c r="G60">
-        <v>-7.944532466717454</v>
+        <v>-9.477947365598014</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.97536498702722</v>
       </c>
       <c r="E61">
-        <v>-8.373779974777159</v>
+        <v>-8.647105080458118</v>
       </c>
       <c r="F61">
-        <v>6.842491825716941</v>
+        <v>6.789626138553657</v>
       </c>
       <c r="G61">
-        <v>-7.874868656934571</v>
+        <v>-9.525569563180431</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.86862366101471</v>
       </c>
       <c r="E62">
-        <v>-8.434013207553182</v>
+        <v>-9.803179209876284</v>
       </c>
       <c r="F62">
-        <v>6.710496272488725</v>
+        <v>7.34821980310605</v>
       </c>
       <c r="G62">
-        <v>-8.157086043066361</v>
+        <v>-9.653306962813209</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.73932516747625</v>
       </c>
       <c r="E63">
-        <v>-8.082916089264492</v>
+        <v>-9.977140538880942</v>
       </c>
       <c r="F63">
-        <v>6.493420870071271</v>
+        <v>7.319966489574611</v>
       </c>
       <c r="G63">
-        <v>-8.440366114316257</v>
+        <v>-9.519812524487637</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.59742469163595</v>
       </c>
       <c r="E64">
-        <v>-7.180975392682779</v>
+        <v>-9.210533288018457</v>
       </c>
       <c r="F64">
-        <v>6.499659087672186</v>
+        <v>7.51075237379577</v>
       </c>
       <c r="G64">
-        <v>-8.352447956429831</v>
+        <v>-10.03958803742645</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.43947589824638</v>
       </c>
       <c r="E65">
-        <v>-6.868805036964023</v>
+        <v>-8.900939634010065</v>
       </c>
       <c r="F65">
-        <v>6.455212381155379</v>
+        <v>7.361041486197449</v>
       </c>
       <c r="G65">
-        <v>-9.122417948499065</v>
+        <v>-10.85246269968464</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.2645497451381</v>
       </c>
       <c r="E66">
-        <v>-7.472264954752167</v>
+        <v>-8.349561695784137</v>
       </c>
       <c r="F66">
-        <v>6.680969659401272</v>
+        <v>7.60899281914231</v>
       </c>
       <c r="G66">
-        <v>-8.593031921859748</v>
+        <v>-9.84535833063741</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.08218236314755</v>
       </c>
       <c r="E67">
-        <v>-7.801779365920301</v>
+        <v>-8.617208095059478</v>
       </c>
       <c r="F67">
-        <v>6.569674726193765</v>
+        <v>7.162801098232316</v>
       </c>
       <c r="G67">
-        <v>-9.41569255673202</v>
+        <v>-9.730234109509254</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.882660842143943</v>
       </c>
       <c r="E68">
-        <v>-7.588406727626889</v>
+        <v>-8.276617036468584</v>
       </c>
       <c r="F68">
-        <v>6.595134382490369</v>
+        <v>6.552849434548136</v>
       </c>
       <c r="G68">
-        <v>-8.868267367449215</v>
+        <v>-9.699406309447561</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.676921464172159</v>
       </c>
       <c r="E69">
-        <v>-7.942542451974727</v>
+        <v>-9.987959063285265</v>
       </c>
       <c r="F69">
-        <v>6.340029449925468</v>
+        <v>6.909265618229615</v>
       </c>
       <c r="G69">
-        <v>-8.705663302196832</v>
+        <v>-9.576469200846725</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.456260878571094</v>
       </c>
       <c r="E70">
-        <v>-7.89685467771134</v>
+        <v>-7.719184528494401</v>
       </c>
       <c r="F70">
-        <v>6.064227064751687</v>
+        <v>6.768542261701412</v>
       </c>
       <c r="G70">
-        <v>-8.619599049812399</v>
+        <v>-8.810836023433938</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.22491803346878</v>
       </c>
       <c r="E71">
-        <v>-7.186536358764198</v>
+        <v>-9.070535514071327</v>
       </c>
       <c r="F71">
-        <v>6.170257759496274</v>
+        <v>6.688542941088903</v>
       </c>
       <c r="G71">
-        <v>-8.586020186407572</v>
+        <v>-9.814825169128712</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.986755772408316</v>
       </c>
       <c r="E72">
-        <v>-8.359071491200245</v>
+        <v>-9.663380688785493</v>
       </c>
       <c r="F72">
-        <v>6.024289168976136</v>
+        <v>6.75357940821234</v>
       </c>
       <c r="G72">
-        <v>-8.032814784613199</v>
+        <v>-9.213812179201723</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.734276714547359</v>
       </c>
       <c r="E73">
-        <v>-8.791875866009333</v>
+        <v>-8.156875126757765</v>
       </c>
       <c r="F73">
-        <v>5.880590029032822</v>
+        <v>6.43824138856553</v>
       </c>
       <c r="G73">
-        <v>-8.51375759837636</v>
+        <v>-9.210435422751667</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.477672646720205</v>
       </c>
       <c r="E74">
-        <v>-7.934549695351188</v>
+        <v>-9.276236917395746</v>
       </c>
       <c r="F74">
-        <v>6.249674276331901</v>
+        <v>6.437354513252883</v>
       </c>
       <c r="G74">
-        <v>-7.748875914800988</v>
+        <v>-8.757738183529568</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.20689580779012</v>
       </c>
       <c r="E75">
-        <v>-8.799347848121988</v>
+        <v>-10.09925989744579</v>
       </c>
       <c r="F75">
-        <v>6.014389423298724</v>
+        <v>6.787293339740215</v>
       </c>
       <c r="G75">
-        <v>-7.956854317214622</v>
+        <v>-8.872796193746938</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.925997067716195</v>
       </c>
       <c r="E76">
-        <v>-7.729876255626511</v>
+        <v>-10.05902893436164</v>
       </c>
       <c r="F76">
-        <v>5.763075882695384</v>
+        <v>6.668981005621395</v>
       </c>
       <c r="G76">
-        <v>-8.149061280679167</v>
+        <v>-9.017321369809361</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.631698652765214</v>
       </c>
       <c r="E77">
-        <v>-9.77031607400262</v>
+        <v>-9.651665526527649</v>
       </c>
       <c r="F77">
-        <v>5.754061428624703</v>
+        <v>5.92389805099643</v>
       </c>
       <c r="G77">
-        <v>-8.323983885883179</v>
+        <v>-7.696920213107665</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.316778199055701</v>
       </c>
       <c r="E78">
-        <v>-10.28538017916104</v>
+        <v>-11.50516993786713</v>
       </c>
       <c r="F78">
-        <v>5.614343725352804</v>
+        <v>5.954188010335124</v>
       </c>
       <c r="G78">
-        <v>-7.464367631156022</v>
+        <v>-7.511347582903819</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.986395373937683</v>
       </c>
       <c r="E79">
-        <v>-10.62626106008843</v>
+        <v>-12.35052282324899</v>
       </c>
       <c r="F79">
-        <v>5.771529704872</v>
+        <v>6.2118854694836</v>
       </c>
       <c r="G79">
-        <v>-7.842259783372749</v>
+        <v>-7.83907834910951</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.630060729101013</v>
       </c>
       <c r="E80">
-        <v>-11.63904521495589</v>
+        <v>-11.55979691982165</v>
       </c>
       <c r="F80">
-        <v>5.601591725321685</v>
+        <v>5.969591134068688</v>
       </c>
       <c r="G80">
-        <v>-6.931005639324041</v>
+        <v>-7.583328774564193</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.251416517940451</v>
       </c>
       <c r="E81">
-        <v>-10.38768293546832</v>
+        <v>-12.88418537115691</v>
       </c>
       <c r="F81">
-        <v>5.724542734066827</v>
+        <v>5.907853526367112</v>
       </c>
       <c r="G81">
-        <v>-7.233665644160831</v>
+        <v>-7.604569234744156</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.844824877682916</v>
       </c>
       <c r="E82">
-        <v>-12.09268962714827</v>
+        <v>-14.04516383792538</v>
       </c>
       <c r="F82">
-        <v>5.426077517243109</v>
+        <v>5.774969514120334</v>
       </c>
       <c r="G82">
-        <v>-5.605658527586675</v>
+        <v>-6.974824020081835</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.4087215938018</v>
       </c>
       <c r="E83">
-        <v>-13.67767364372893</v>
+        <v>-12.16740944827483</v>
       </c>
       <c r="F83">
-        <v>5.344239514062775</v>
+        <v>5.620117917120496</v>
       </c>
       <c r="G83">
-        <v>-6.235377257884683</v>
+        <v>-6.287227022120748</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.948221673978284</v>
       </c>
       <c r="E84">
-        <v>-14.59902790838152</v>
+        <v>-14.82733092547822</v>
       </c>
       <c r="F84">
-        <v>5.535091913932383</v>
+        <v>6.01552652414601</v>
       </c>
       <c r="G84">
-        <v>-5.727201896515477</v>
+        <v>-6.743982990173993</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.460651475578243</v>
       </c>
       <c r="E85">
-        <v>-15.2806719299121</v>
+        <v>-16.48797668577904</v>
       </c>
       <c r="F85">
-        <v>5.11555554728515</v>
+        <v>5.607820440687109</v>
       </c>
       <c r="G85">
-        <v>-4.834049815475503</v>
+        <v>-6.561899674968539</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.958821227275318</v>
       </c>
       <c r="E86">
-        <v>-17.08015617481407</v>
+        <v>-18.34584654606191</v>
       </c>
       <c r="F86">
-        <v>5.228130114872332</v>
+        <v>5.72302079268209</v>
       </c>
       <c r="G86">
-        <v>-5.488352656948139</v>
+        <v>-6.074037821028301</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.447278049316091</v>
       </c>
       <c r="E87">
-        <v>-17.24036452825743</v>
+        <v>-17.89618719099627</v>
       </c>
       <c r="F87">
-        <v>5.092965566107321</v>
+        <v>5.770250070492325</v>
       </c>
       <c r="G87">
-        <v>-4.641270127632664</v>
+        <v>-4.81262396474534</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.938631568205254</v>
       </c>
       <c r="E88">
-        <v>-18.65749612726978</v>
+        <v>-20.02245970571376</v>
       </c>
       <c r="F88">
-        <v>4.725916380909583</v>
+        <v>5.232724445733022</v>
       </c>
       <c r="G88">
-        <v>-4.202060050937555</v>
+        <v>-4.899045756048015</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.446666651230019</v>
       </c>
       <c r="E89">
-        <v>-20.48030201331126</v>
+        <v>-21.80969442842499</v>
       </c>
       <c r="F89">
-        <v>4.538836368530552</v>
+        <v>5.604656196268061</v>
       </c>
       <c r="G89">
-        <v>-4.483006187582265</v>
+        <v>-4.407846872204192</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.979743076597135</v>
       </c>
       <c r="E90">
-        <v>-20.71647098975929</v>
+        <v>-23.04889775520196</v>
       </c>
       <c r="F90">
-        <v>4.39943540644174</v>
+        <v>5.225957270356349</v>
       </c>
       <c r="G90">
-        <v>-3.585335211881187</v>
+        <v>-2.96310493559301</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.555752998859016</v>
       </c>
       <c r="E91">
-        <v>-22.4318478869168</v>
+        <v>-25.39360574215345</v>
       </c>
       <c r="F91">
-        <v>4.396020936488053</v>
+        <v>5.237809725427498</v>
       </c>
       <c r="G91">
-        <v>-3.102584840253583</v>
+        <v>-2.829418485626161</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.180509212269343</v>
       </c>
       <c r="E92">
-        <v>-24.15393145407968</v>
+        <v>-26.23325727875965</v>
       </c>
       <c r="F92">
-        <v>4.155338813695058</v>
+        <v>4.226870058777712</v>
       </c>
       <c r="G92">
-        <v>-2.980425709854477</v>
+        <v>-1.982375682857156</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.864990891484094</v>
       </c>
       <c r="E93">
-        <v>-27.61463657548144</v>
+        <v>-28.74397459435832</v>
       </c>
       <c r="F93">
-        <v>3.79090432696371</v>
+        <v>4.544594723239089</v>
       </c>
       <c r="G93">
-        <v>-2.701412931804701</v>
+        <v>-2.823495919656405</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.6130756395246708</v>
       </c>
       <c r="E94">
-        <v>-29.00162212302473</v>
+        <v>-30.92470427325506</v>
       </c>
       <c r="F94">
-        <v>3.370153257879335</v>
+        <v>4.080195135419288</v>
       </c>
       <c r="G94">
-        <v>-2.342003555333725</v>
+        <v>-2.41234271640662</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4249783811441993</v>
       </c>
       <c r="E95">
-        <v>-30.1980245777182</v>
+        <v>-30.99178908720468</v>
       </c>
       <c r="F95">
-        <v>2.811776561037356</v>
+        <v>3.735517379983047</v>
       </c>
       <c r="G95">
-        <v>-2.653208078207373</v>
+        <v>-2.643508179777309</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.301214048104776</v>
       </c>
       <c r="E96">
-        <v>-32.78040499448825</v>
+        <v>-34.92101918638804</v>
       </c>
       <c r="F96">
-        <v>2.760744805324151</v>
+        <v>3.328810614956788</v>
       </c>
       <c r="G96">
-        <v>-1.265834585246222</v>
+        <v>-0.7620655599897863</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.2317452343320958</v>
       </c>
       <c r="E97">
-        <v>-34.67269352146642</v>
+        <v>-36.87283450419704</v>
       </c>
       <c r="F97">
-        <v>2.432133746400043</v>
+        <v>2.945308309003549</v>
       </c>
       <c r="G97">
-        <v>-1.574211902229333</v>
+        <v>-1.696228679170251</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2095475516942422</v>
       </c>
       <c r="E98">
-        <v>-36.34675262177795</v>
+        <v>-38.44448669329911</v>
       </c>
       <c r="F98">
-        <v>1.641593680884218</v>
+        <v>2.908374703349585</v>
       </c>
       <c r="G98">
-        <v>-1.801153109491912</v>
+        <v>-2.274518084515682</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.2175684128287676</v>
       </c>
       <c r="E99">
-        <v>-38.56772458494385</v>
+        <v>-41.06002912522733</v>
       </c>
       <c r="F99">
-        <v>1.655018755929399</v>
+        <v>1.896714450508274</v>
       </c>
       <c r="G99">
-        <v>-1.828984865840565</v>
+        <v>-1.171649564653957</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.2402273155942564</v>
       </c>
       <c r="E100">
-        <v>-40.66010600018794</v>
+        <v>-43.51837237469029</v>
       </c>
       <c r="F100">
-        <v>1.174753602248724</v>
+        <v>1.709637605541074</v>
       </c>
       <c r="G100">
-        <v>-2.187612953564273</v>
+        <v>-3.80303668654366</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.2544915247255002</v>
       </c>
       <c r="E101">
-        <v>-42.65584072316032</v>
+        <v>-43.12427060298776</v>
       </c>
       <c r="F101">
-        <v>1.117217566340809</v>
+        <v>1.530206892733616</v>
       </c>
       <c r="G101">
-        <v>-2.415050742657743</v>
+        <v>-2.018897621246396</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.2440228453523433</v>
       </c>
       <c r="E102">
-        <v>-44.83367444292916</v>
+        <v>-48.02945251369719</v>
       </c>
       <c r="F102">
-        <v>0.7717954691243114</v>
+        <v>0.6127280469775733</v>
       </c>
       <c r="G102">
-        <v>-2.295778407968881</v>
+        <v>-2.246484384889133</v>
       </c>
     </row>
   </sheetData>
